--- a/www/download/COUNTRY.RUS.WIOD16.xlsx
+++ b/www/download/COUNTRY.RUS.WIOD16.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>Rússia</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,1848 +852,3409 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>28.1269424922751</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.081</t>
+          <t>29.1577492315846</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>31.2592801846091</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.103</t>
+          <t>30.6755992277201</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>28.8090621516598</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.155</t>
+          <t>28.2790235052344</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.187</t>
+          <t>27.1762023719573</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.248</t>
+          <t>25.565443588361</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.307</t>
+          <t>24.7644284230225</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.262</t>
+          <t>31.6246533382754</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0.317</t>
+          <t>30.3573975839266</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0.373</t>
+          <t>29.3223316036304</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0.396</t>
+          <t>30.745013118545</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0.407</t>
+          <t>31.8057054506009</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>37.6190172116849</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>74.224</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>74.475</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>75.271</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>76.473</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>76.753</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>77.33</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>77.804</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>78.633</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>78.997</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>76.285</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>76.443</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>76.03</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>77.252</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>75.121</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>74.289</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>61.676</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>61.586</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>61.853</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>62.315</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>62.536</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>63.509</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>63.876</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>64.55</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>64.781</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>62.384</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>62.203</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>61.953</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>62.965</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>61.07</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>60.265</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>136541.52</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>136046.652</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>136983.091</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>138344.327</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>139714.335</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>141561.856</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>143026.816</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>144464.258</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>138811.358</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>134351.527</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>135336.087</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>134430.087</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>136550.786</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>133217.91</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>132151.049</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>113791.683</t>
+          <t>158390576495.053</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>112933.372</t>
+          <t>158463029228.886</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>113069.898</t>
+          <t>155860425670.173</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>113275.945</t>
+          <t>157998742516.547</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>114351.922</t>
+          <t>151880443654.725</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>116707.602</t>
+          <t>155058242181.226</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>117843.623</t>
+          <t>153973669647.667</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>119010.842</t>
+          <t>154132963545.921</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>111583.096</t>
+          <t>144935804316.612</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>107752.964</t>
+          <t>138899429446.223</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>107975.668</t>
+          <t>140370291485.231</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>107391.548</t>
+          <t>140079428225.502</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>109117.823</t>
+          <t>143643794913.822</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>106107.939</t>
+          <t>138108469179.355</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>104932.646</t>
+          <t>128991411187.391</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>44598332642.8781</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>44755613499.9693</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>46817255469.9241</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>50944761065.5864</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>53930404750.7182</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>56400962183.7704</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>57315554263.846</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>62606176261.7769</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>59020018090.6854</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>59648945625.9844</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>64359539831.3348</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>63389782792.0459</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>69794770159.7811</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>69422655936.7061</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>59864133532.5563</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>11586261.8324074</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>9542572.53803021</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>8483813.71645606</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>7283086.87948664</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>5277359.68613592</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>4405681.31591996</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>3464696.79876643</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>2617082.17028452</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>1931969.14868893</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>2450799.08647256</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>2121393.22063344</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>1723160.11208849</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>1721114.91366652</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>1581132.18358462</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>1605764.4627739</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>781741.654652653</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>759927.691364473</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>760879.605698521</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>827338.399232127</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>913445.51646786</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>984788.333133858</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>1045416.00945549</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>1181515.80536361</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>1166959.21906576</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>998675.210259065</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>1106543.94807938</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>1144180.85354862</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>1137791.31182203</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>1082145.97431977</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>1048165.79681284</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>1286981.43118862</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1275467.92458565</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>1262049.21732588</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>1392327.52779567</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>1479720.22636252</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>1621983.80288407</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>1701534.68117358</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>1923131.65539531</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>1962813.48494936</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>1711834.76156452</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>1916593.73970827</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>2031140.93270274</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>2029399.6560179</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>1949257.18439902</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>1829012.99024575</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>1.55147841313237</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1.52333424052108</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>1.41513298601276</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>1.22350527572734</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>1.12036090825885</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>1.0692484220346</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>1.05604961015503</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>0.900944109769247</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>0.890597455062628</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>0.806452115275285</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>0.677694841867558</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>0.694146016437768</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>0.56340973328226</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>0.528433874623589</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>0.752846651374881</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>72410.652190693</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>80760.2882142641</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>87182.5529060631</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>103209.430774678</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>132549.787033459</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>155445.532012455</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>187438.566082529</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>247282.397833211</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>307144.516822803</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>262314.957509309</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>316151.193680319</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>371829.458831327</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>396066.593880761</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>407191.885318571</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>360243.057461838</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>28.1269424922751</t>
+          <t>723.101274912144</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>29.1577492315846</t>
+          <t>726.713330044985</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>31.2592801846091</t>
+          <t>756.91382725978</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>30.6755992277201</t>
+          <t>817.537159650702</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>28.8090621516598</t>
+          <t>862.38324434262</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>28.2790235052344</t>
+          <t>888.076287849184</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>27.1762023719573</t>
+          <t>897.29817254538</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>25.565443588361</t>
+          <t>969.893964204418</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>24.7644284230225</t>
+          <t>911.073863086223</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>31.6246533382754</t>
+          <t>956.154463528705</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>30.3573975839266</t>
+          <t>1034.67387735771</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>29.3223316036304</t>
+          <t>1023.1956916332</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>30.745013118545</t>
+          <t>1108.47316628928</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>31.8057054506009</t>
+          <t>1136.76667844009</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>37.6190172116849</t>
+          <t>993.345501543384</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>-837800157.547845</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.113</t>
+          <t>2983276544.07475</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>4346691708.67592</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.169</t>
+          <t>8108246101.30938</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.236</t>
+          <t>15323812664.3269</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>22778663248.9761</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.376</t>
+          <t>25573516879.5145</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.512</t>
+          <t>30901552790.5115</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.617</t>
+          <t>38030649549.3982</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.488</t>
+          <t>34876192173.2024</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>0.576</t>
+          <t>42960686701.8391</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>0.698</t>
+          <t>47518030133.6857</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>0.771</t>
+          <t>53676273183.9511</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>0.815</t>
+          <t>56152584512.392</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>0.755</t>
+          <t>46673834192.2964</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>-3765980332.14006</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>369693705.35471</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.167</t>
+          <t>1450909257.35964</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.212</t>
+          <t>4529132521.47235</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.291</t>
+          <t>11901967538.019</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.358</t>
+          <t>18575888754.4787</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.464</t>
+          <t>20069265470.8342</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.634</t>
+          <t>25408633691.3175</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.838</t>
+          <t>29956555386.4667</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.663</t>
+          <t>29937103495.9255</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>0.783</t>
+          <t>37534678390.1247</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>0.948</t>
+          <t>40573001276.7663</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>1.048</t>
+          <t>47304921092.3477</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>1.108</t>
+          <t>50346769799.1492</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>1.027</t>
+          <t>41695394036.3943</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>2928180174.59221</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.011</t>
+          <t>2613582838.72004</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.081</t>
+          <t>2895782451.31628</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>1.244</t>
+          <t>3579113579.83703</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>1.567</t>
+          <t>3421845126.30793</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>1.849</t>
+          <t>4202774494.49743</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2.252</t>
+          <t>5504251408.68029</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>2.958</t>
+          <t>5492919099.19397</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>3.778</t>
+          <t>8074094162.93151</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>4939088677.27687</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>3.675</t>
+          <t>5426008311.71435</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>4.322</t>
+          <t>6945028856.91941</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>4.64</t>
+          <t>6371352091.60343</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>4.934</t>
+          <t>5805814713.2428</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>4.649</t>
+          <t>4978440155.90209</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.446</t>
+          <t>1844.97729344683</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.546</t>
+          <t>1833.74062874561</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.608</t>
+          <t>1828.04755178426</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.759</t>
+          <t>1817.79818758648</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>1.024</t>
+          <t>1828.56371924153</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>1.309</t>
+          <t>1837.65045727827</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>1.701</t>
+          <t>1844.88955785475</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>2.259</t>
+          <t>1843.71421835513</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2.892</t>
+          <t>1722.47392692489</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2.186</t>
+          <t>1727.24725317134</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2.635</t>
+          <t>1735.86702705814</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>3.263</t>
+          <t>1733.44290501667</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>3.416</t>
+          <t>1732.99773725887</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>3.631</t>
+          <t>1737.47269887117</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>3.381</t>
+          <t>1741.18233603862</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.233</t>
+          <t>1839.57668904076</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.274</t>
+          <t>1826.75322813659</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.312</t>
+          <t>1819.87053108274</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.379</t>
+          <t>1809.06388596914</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.516</t>
+          <t>1820.30584145164</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.655</t>
+          <t>1830.61906322396</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.845</t>
+          <t>1838.28603653459</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>1.114</t>
+          <t>1837.19701818367</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>1.428</t>
+          <t>1757.1715629369</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>1.081</t>
+          <t>1761.16873652956</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1.296</t>
+          <t>1770.41592725023</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>1.604</t>
+          <t>1768.12913801418</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>1.723</t>
+          <t>1767.60849057248</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>1.789</t>
+          <t>1773.38208805616</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>1.624</t>
+          <t>1778.88374027117</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>97977.4178306694</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>94552.0949544822</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>104540.715196485</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>130925.848273172</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>173339.16986369</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>228603.088520377</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>286582.902567303</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>339335.133150673</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>454519.919047535</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>301555.467166357</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>390018.767687349</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>500414.339598897</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>516076.803881571</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>518834.772562219</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>493789.092159467</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>22850120400.027</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>19345235474.9765</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>19642991678.7016</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>19334890141.9737</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>16696070168.7666</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>17258475721.7984</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>16609748882.5245</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>16054230152.9168</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>14059487283.3406</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>13078971583.3428</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>13462816046.1659</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>14005404450.4657</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>15164834204.7893</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>14965916161.173</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>15359950551.5137</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>50751.8141405603</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>60004.76603045</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>70733.7817717708</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>87138.7015560464</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>109987.875805261</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>139867.745922899</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>181123.508377434</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>245752.116726886</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>324813.517441093</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>216458.365723909</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>280210.085746297</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>364024.587923381</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>394721.424436842</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>413860.502795611</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>378879.48919823</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>136541.52</t>
+          <t>14715919684.0526</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>136046.652</t>
+          <t>16797833963.2479</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>136983.091</t>
+          <t>18530689719.6585</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>138344.327</t>
+          <t>20781071437.4992</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>139714.335</t>
+          <t>23277721877.5026</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>141561.856</t>
+          <t>28848316042.3966</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>143026.816</t>
+          <t>30080012332.8589</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>144464.258</t>
+          <t>37803298324.49</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>138811.358</t>
+          <t>40923520226.0207</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>134351.527</t>
+          <t>39670974507.5526</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>135336.087</t>
+          <t>46926942760.6919</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>134430.087</t>
+          <t>50332747723.4525</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>136550.786</t>
+          <t>58777220921.8101</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>133217.91</t>
+          <t>62364685457.0223</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>132151.049</t>
+          <t>52545001681.1535</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>113791.683</t>
+          <t>47225.603690109</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>112933.372</t>
+          <t>34547.3289240322</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>113069.898</t>
+          <t>33806.9334247143</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>113275.945</t>
+          <t>43787.1467171257</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>114351.922</t>
+          <t>63351.2940584285</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>116707.602</t>
+          <t>88735.3425974783</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>117843.623</t>
+          <t>105459.394189869</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>119010.842</t>
+          <t>93583.0164237868</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>111583.096</t>
+          <t>129706.401606442</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>107752.964</t>
+          <t>85097.1014424475</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>107975.668</t>
+          <t>109808.681941052</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>107391.548</t>
+          <t>136389.751675516</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>109117.823</t>
+          <t>121355.379444729</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>106107.939</t>
+          <t>104974.269766609</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>104932.646</t>
+          <t>114909.602961237</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>158393.773</t>
+          <t>8134200715.97439</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>158486.666</t>
+          <t>2547401511.72857</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>155881.96</t>
+          <t>1112301959.04311</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>158003.526</t>
+          <t>-1446181295.5255</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>151889.552</t>
+          <t>-6581651708.73599</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>155065.262</t>
+          <t>-11589840320.5982</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>153985.616</t>
+          <t>-13470263450.3344</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>154148.048</t>
+          <t>-21749068171.5732</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>144935.907</t>
+          <t>-26864032942.6801</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>138909.145</t>
+          <t>-26592002924.2099</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>140394.951</t>
+          <t>-33464126714.526</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>140108.613</t>
+          <t>-36327343272.9867</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>143654.52</t>
+          <t>-43612386717.0208</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>138107.476</t>
+          <t>-47398769295.8493</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>128984.343</t>
+          <t>-37185051129.6397</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>1.287</t>
+          <t>127594.760144944</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1.275</t>
+          <t>145315.186227776</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>1.262</t>
+          <t>163395.081006747</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>1.392</t>
+          <t>195079.15792392</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>283801.03626121</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>1.622</t>
+          <t>361678.99189653</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>1.702</t>
+          <t>455102.72715222</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>1.923</t>
+          <t>584467.62257373</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>1.963</t>
+          <t>736187.7497784</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>1.712</t>
+          <t>535212.94704951</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>647808.866111974</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>2.031</t>
+          <t>825357.531192619</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>2.029</t>
+          <t>873174.153606371</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>1.949</t>
+          <t>892471.792419621</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>1.829</t>
+          <t>797891.010999408</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>96210.022</t>
+          <t>0.0511331379612469</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>94412.758</t>
+          <t>0.0520788283267562</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>93967.032</t>
+          <t>0.0528796435291925</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>93884.825</t>
+          <t>0.0510353811799919</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>93757.258</t>
+          <t>0.0586268397466521</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>94143.695</t>
+          <t>0.0766582942524178</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>94600.798</t>
+          <t>0.0860511836077626</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>94694.782</t>
+          <t>0.0787224467232124</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>86169.254</t>
+          <t>0.0749690714120067</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>81033.181</t>
+          <t>0.0504156923374682</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>81042.682</t>
+          <t>0.0536048999949558</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>78909.443</t>
+          <t>0.0656212017169532</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>80534.488</t>
+          <t>0.0601957621360465</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>76672.04</t>
+          <t>0.0555626235241563</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>73922.048</t>
+          <t>0.0509531302520956</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.782</t>
+          <t>92578.4111864287</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>113136.154108597</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.761</t>
+          <t>134550.188450465</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.827</t>
+          <t>169464.783615425</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.913</t>
+          <t>235805.054083951</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.985</t>
+          <t>289567.341927265</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>1.045</t>
+          <t>375750.442596114</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>1.181</t>
+          <t>512270.390450192</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>1.167</t>
+          <t>616519.353154551</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.999</t>
+          <t>487965.085549919</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1.106</t>
+          <t>576231.516526235</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>1.144</t>
+          <t>697566.227672211</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>1.138</t>
+          <t>770919.341032159</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>1.082</t>
+          <t>814770.693943947</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>1.048</t>
+          <t>755385.270610665</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>44599.48</t>
+          <t>114157.265587553</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>44759.562</t>
+          <t>140292.566269018</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>46820.961</t>
+          <t>167393.480441693</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>50946.889</t>
+          <t>212108.033004503</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>53930.817</t>
+          <t>291357.79391856</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>56402.903</t>
+          <t>357623.831331478</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>57320.655</t>
+          <t>464258.700883244</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>62611.907</t>
+          <t>634045.000969024</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>59015.029</t>
+          <t>838027.66291</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>59649.838</t>
+          <t>663285.324091058</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>64364.412</t>
+          <t>783264.866852056</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>63396.06</t>
+          <t>948193.750885118</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>69798.126</t>
+          <t>1047901.78999335</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>69422.697</t>
+          <t>1107508.43141786</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>59862.93</t>
+          <t>1026786.50477773</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>155.14</t>
+          <t>900289.312167438</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>152.31</t>
+          <t>1011315.26768526</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>141.49</t>
+          <t>1080682.59854099</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>122.34</t>
+          <t>1243785.8260353</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>112.03</t>
+          <t>1566851.4496426</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>106.92</t>
+          <t>1849121.18360728</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>105.59</t>
+          <t>2252121.7569958</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>90.08</t>
+          <t>2957876.22634916</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>89.08</t>
+          <t>3777705.66350131</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>80.64</t>
+          <t>3089859.86436662</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>67.76</t>
+          <t>3675424.27180718</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>69.4</t>
+          <t>4321715.08929451</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>56.33</t>
+          <t>4640419.48795297</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>52.84</t>
+          <t>4934341.71216641</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>75.29</t>
+          <t>4648715.19728378</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>11.586</t>
+          <t>516225.567253399</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>9.544</t>
+          <t>538933.734972823</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>8.485</t>
+          <t>576852.36973943</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>7.283</t>
+          <t>618993.355842504</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>5.278</t>
+          <t>668474.972974702</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>4.406</t>
+          <t>689994.466633925</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>3.465</t>
+          <t>742182.296685738</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>2.617</t>
+          <t>824151.743373823</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>1.932</t>
+          <t>888040.032209569</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>2.451</t>
+          <t>848255.434196542</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>2.122</t>
+          <t>845377.449748755</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>1.724</t>
+          <t>852725.532020347</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>1.721</t>
+          <t>910348.261701263</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>1.581</t>
+          <t>924532.866812323</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>1.606</t>
+          <t>932734.671591207</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>428024.80682654</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>443290.440651273</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>471484.192236049</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>507649.592412134</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>553515.492224759</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>566006.365028603</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>605998.439508909</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>670276.682293706</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>653312.402595326</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>624043.711337203</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>621926.439600943</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>627332.263881233</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>669724.098384978</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>680159.413927595</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>686193.312012691</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>118445.269794787</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>133428.402424272</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>144328.663485112</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>166686.514512661</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>224409.335878465</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>297196.007813801</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>381236.308900811</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>480133.651475839</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>590355.602483375</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>418092.381797108</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>513171.944209577</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>655425.596469123</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>675400.181589052</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>681356.856211214</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>597109.648413934</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>113791683000</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>112933372000</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>113069898000</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>113275945000</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>114351922000</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>116707602000</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>117843623000</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>119010842000</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>111583096000</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>107752964000</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>107975668000</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>107391548000</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>109117823000</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>106107939000</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>104932646000</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>136541520147.878</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>136046652027.818</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>136983090752.447</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>138344327273.116</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>139714334716.223</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>141561856367.585</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>143026815632.393</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>144464258014.926</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>138811357515.703</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>134351526696.895</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>135336087079.63</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>134430087458.914</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>136550785577.677</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>133217909534.563</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>132151049460.07</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>96210021644.4255</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>94412757582.7893</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>93967032030.0215</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>93884825304.9212</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>93757257503.0607</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>94143694644.0518</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>94600798364.7208</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>94694781839.8861</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>86169253633.5643</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>81033181485.5148</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>81042681771.862</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>78909443048.0438</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>80534487805.5157</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>76672039553.3559</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>73922047579.9231</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>74224424</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>74474565</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>75270789</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>76472881</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>76753220</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>77330046</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>77804440</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>78632970</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>78997043</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>76285437</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>76443103</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>76029564</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>77251714</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>75120816</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>74288750</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>61676468</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>61586339</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>61852821</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>62314918</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>62536471</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>63509141</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>63875706</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>64549506</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>64780717</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>62384215</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>62202730</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>61952746</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>62964781</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>61070277</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>60265168</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>136541520147.878</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>136046652027.818</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>136983090752.447</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>138344327273.116</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>139714334716.223</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>141561856367.585</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>143026815632.393</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>144464258014.926</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>138811357515.703</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>134351526696.895</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>135336087079.63</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>134430087458.914</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>136550785577.677</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>133217909534.563</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>132151049460.07</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>113791683000</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>112933372000</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>113069898000</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>113275945000</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>114351922000</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>116707602000</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>117843623000</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>119010842000</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>111583096000</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>107752964000</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>107975668000</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>107391548000</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>109117823000</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>106107939000</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>104932646000</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>446270.03779127</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>546091.11494636</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>607515.54866235</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>758684.08618872</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>1023657.84825538</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>1309118.82232761</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>1700894.99321385</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>2258991.98837725</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>2891627.8589355</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>2185970.34762696</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>2635097.87335472</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>3262680.41250156</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>3415630.89062014</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>3630523.90256947</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>3381079.3674049</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>232602.535880084</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>273720.967630108</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>311722.145334387</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>378794.54768016</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>515767.12938049</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>654819.83918064</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>845495.01103515</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>1114178.64806395</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>1428383.2626475</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>1081377.71059968</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>1296436.81300515</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>1603619.35328828</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>1723301.96855752</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>1788865.28847798</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>1623896.15686002</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>4231770.43381166</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>3914287.61132449</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>3755997.51854662</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>3541328.7757302</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>3605338.82778093</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>3489306.50055324</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>3555379.60774921</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>3772769.30220159</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>3943683.69979092</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>3900633.80410518</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>3966883.92778593</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>4026041.90800838</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>4157136.26200617</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>4269604.21965658</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>4479152.31014657</t>
         </is>
       </c>
     </row>
@@ -2699,7 +4265,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2722,36 +4288,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -2763,331 +4344,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3124,6 +5069,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>WIOD16</t>
